--- a/tasks/finalpool/yt-train-conference-planning-notion-gcal-excel/groundtruth_workspace/Conference_Planning.xlsx
+++ b/tasks/finalpool/yt-train-conference-planning-notion-gcal-excel/groundtruth_workspace/Conference_Planning.xlsx
@@ -514,19 +514,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>b0XI-cbel1U</t>
+          <t>QYVucud3ptc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Is Elon's Grok 3 the new AI king?</t>
+          <t>Wake up babe, a dangerous new open-source AI model is here</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1582069</v>
+        <v>1601016</v>
       </c>
       <c r="E5" t="n">
-        <v>244</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6">
@@ -535,19 +535,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QYVucud3ptc</t>
+          <t>b0XI-cbel1U</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wake up babe, a dangerous new open-source AI model is here</t>
+          <t>Is Elon's Grok 3 the new AI king?</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1601016</v>
+        <v>1582069</v>
       </c>
       <c r="E6" t="n">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
